--- a/ga_results.xlsx
+++ b/ga_results.xlsx
@@ -1,37 +1,361 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PERSONAL\BRYAN\bulsu\Thesis 1\ShelterAlloc_Thesis\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{615B0E57-76CA-4BD7-9CED-D608BFE0A835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GA Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WORK" sheetId="1" r:id="rId1"/>
+    <sheet name="BNST" sheetId="2" r:id="rId2"/>
+    <sheet name="BNT" sheetId="3" r:id="rId3"/>
+    <sheet name="BST" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="103">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Fitness</t>
+  </si>
+  <si>
+    <t>Gen Last Updated</t>
+  </si>
+  <si>
+    <t>Runtime</t>
+  </si>
+  <si>
+    <t>Allocation</t>
+  </si>
+  <si>
+    <t>202500000000000040894464</t>
+  </si>
+  <si>
+    <t>1m 58.15s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Santa Clara Brgy. Hall', 'Banga &amp; San Guillermo': 'Suplang Covered Court', 'Caloocan &amp; Leynes': 'Tagaytay Unida Church', 'Poblacion Barangay 1': 'San Antonio Brgy. Hall', 'Poblacion Barangay 5': 'San Antonio Brgy. Hall', 'Poblacion Barangay 2,3,4,6,7,8': 'San Fernando Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'Darasa Brgy. Hall', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'San Antonio Brgy. Hall', 'Tranca': 'Suplang Covered Court'}}</t>
+  </si>
+  <si>
+    <t>1m 58.13s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Maugat Gymnasium', 'Banga &amp; San Guillermo': 'City EC of Sto. Tomas', 'Caloocan &amp; Leynes': 'Tagaytay Unida Church', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'Tagaytay Unida Church', 'Poblacion Barangay 2,3,4,6,7,8': 'Santa Clara Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'San Fernando Brgy. Hall', 'Sampaloc': 'Brgy. Asis-3 EC', 'Santa Maria, Balas, &amp; Buco': 'Brgy. Asis-3 EC', 'Tranca': 'Tagaytay Unida Church'}}</t>
+  </si>
+  <si>
+    <t>1m 57.78s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Darasa Brgy. Hall', 'Banga &amp; San Guillermo': 'Brgy. Asis-3 EC', 'Caloocan &amp; Leynes': 'Tagaytay Unida Church', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'Maugat Gymnasium', 'Poblacion Barangay 2,3,4,6,7,8': 'San Fernando Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'City EC of Sto. Tomas', 'Sampaloc': 'Maugat Gymnasium', 'Santa Maria, Balas, &amp; Buco': 'Tagaytay Unida Church', 'Tranca': 'Brgy. Asis-3 EC'}}</t>
+  </si>
+  <si>
+    <t>1m 57.72s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Brgy. Asis-3 EC', 'Banga &amp; San Guillermo': 'Suplang Covered Court', 'Caloocan &amp; Leynes': 'Tagaytay Unida Church', 'Poblacion Barangay 1': 'Suplang Covered Court', 'Poblacion Barangay 5': 'Brgy. Asis-3 EC', 'Poblacion Barangay 2,3,4,6,7,8': 'Darasa Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'San Antonio Brgy. Hall', 'Sampaloc': 'Santa Clara Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Santa Clara Brgy. Hall', 'Tranca': 'Tagaytay Unida Church'}}</t>
+  </si>
+  <si>
+    <t>1m 57.61s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'City EC of Sto. Tomas', 'Banga &amp; San Guillermo': 'Brgy. San Jose BB Court', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'Brgy. San Jose BB Court', 'Poblacion Barangay 5': 'City EC of Sto. Tomas', 'Poblacion Barangay 2,3,4,6,7,8': 'San Fernando Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'Maugat Gymnasium', 'Sampaloc': 'Brgy. Asis-3 EC', 'Santa Maria, Balas, &amp; Buco': 'Tagaytay Unida Church', 'Tranca': 'Tagaytay Unida Church'}}</t>
+  </si>
+  <si>
+    <t>1m 57.58s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Brgy. San Jose BB Court', 'Banga &amp; San Guillermo': 'Santa Clara Brgy. Hall', 'Caloocan &amp; Leynes': 'City EC of Sto. Tomas', 'Poblacion Barangay 1': 'Brgy. San Jose BB Court', 'Poblacion Barangay 5': 'City EC of Sto. Tomas', 'Poblacion Barangay 2,3,4,6,7,8': 'Tagaytay Unida Church', 'Quiling, Miranda, &amp; Tumaway': 'San Antonio Brgy. Hall', 'Sampaloc': 'Darasa Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Darasa Brgy. Hall', 'Tranca': 'City EC of Sto. Tomas'}}</t>
+  </si>
+  <si>
+    <t>1m 57.44s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Maugat Gymnasium', 'Banga &amp; San Guillermo': 'Santa Clara Brgy. Hall', 'Caloocan &amp; Leynes': 'Darasa Brgy. Hall', 'Poblacion Barangay 1': 'San Antonio Brgy. Hall', 'Poblacion Barangay 5': 'San Antonio Brgy. Hall', 'Poblacion Barangay 2,3,4,6,7,8': 'San Fernando Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'Suplang Covered Court', 'Sampaloc': 'Darasa Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'San Antonio Brgy. Hall', 'Tranca': 'Santa Clara Brgy. Hall'}}</t>
+  </si>
+  <si>
+    <t>1m 57.56s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Maugat Gymnasium', 'Banga &amp; San Guillermo': 'Santa Clara Brgy. Hall', 'Caloocan &amp; Leynes': 'Brgy. San Jose BB Court', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'Darasa Brgy. Hall', 'Poblacion Barangay 2,3,4,6,7,8': 'Suplang Covered Court', 'Quiling, Miranda, &amp; Tumaway': 'Tagaytay Unida Church', 'Sampaloc': 'Darasa Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Brgy. San Jose BB Court', 'Tranca': 'Santa Clara Brgy. Hall'}}</t>
+  </si>
+  <si>
+    <t>1m 57.92s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Santa Clara Brgy. Hall', 'Banga &amp; San Guillermo': 'Tagaytay Unida Church', 'Caloocan &amp; Leynes': 'San Antonio Brgy. Hall', 'Poblacion Barangay 1': 'San Antonio Brgy. Hall', 'Poblacion Barangay 5': 'Santa Clara Brgy. Hall', 'Poblacion Barangay 2,3,4,6,7,8': 'Brgy. Asis-3 EC', 'Quiling, Miranda, &amp; Tumaway': 'Suplang Covered Court', 'Sampaloc': 'Brgy. San Jose BB Court', 'Santa Maria, Balas, &amp; Buco': 'Brgy. San Jose BB Court', 'Tranca': 'San Antonio Brgy. Hall'}}</t>
+  </si>
+  <si>
+    <t>1m 57.33s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Suplang Covered Court', 'Banga &amp; San Guillermo': 'San Fernando Brgy. Hall', 'Caloocan &amp; Leynes': 'San Fernando Brgy. Hall', 'Poblacion Barangay 1': 'Brgy. Asis-3 EC', 'Poblacion Barangay 5': 'Suplang Covered Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Tagaytay Unida Church', 'Quiling, Miranda, &amp; Tumaway': 'Darasa Brgy. Hall', 'Sampaloc': 'Brgy. Asis-3 EC', 'Santa Maria, Balas, &amp; Buco': 'Maugat Gymnasium', 'Tranca': 'Maugat Gymnasium'}}</t>
+  </si>
+  <si>
+    <t>126736846</t>
+  </si>
+  <si>
+    <t>1m 51.94s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'San Antonio Brgy. Hall', 'Banga &amp; San Guillermo': 'Brgy. San Jose BB Court', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'San Antonio Brgy. Hall', 'Poblacion Barangay 5': 'Brgy. Asis-3 EC', 'Poblacion Barangay 2,3,4,6,7,8': 'Brgy. Asis-3 EC', 'Quiling, Miranda, &amp; Tumaway': 'San Antonio Brgy. Hall', 'Sampaloc': 'Brgy. San Jose BB Court', 'Santa Maria, Balas, &amp; Buco': 'Brgy. San Jose BB Court', 'Tranca': 'Brgy. San Jose BB Court'}, 'transferred': {'Aya': 'San Antonio Brgy. Hall', 'Banga &amp; San Guillermo': 'Brgy. San Jose BB Court', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'San Antonio Brgy. Hall', 'Poblacion Barangay 5': 'Brgy. Asis-3 EC', 'Poblacion Barangay 2,3,4,6,7,8': 'Brgy. Asis-3 EC', 'Quiling, Miranda, &amp; Tumaway': 'San Antonio Brgy. Hall', 'Sampaloc': 'Brgy. San Jose BB Court', 'Santa Maria, Balas, &amp; Buco': 'Brgy. San Jose BB Court', 'Tranca': 'Brgy. San Jose BB Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 2, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 2, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 2, 'Darasa Brgy. Hall': 2, 'Santa Clara Brgy. Hall': 2, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>126895436</t>
+  </si>
+  <si>
+    <t>1m 52.13s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Darasa Brgy. Hall', 'Banga &amp; San Guillermo': 'Darasa Brgy. Hall', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'San Antonio Brgy. Hall', 'Poblacion Barangay 5': 'San Antonio Brgy. Hall', 'Poblacion Barangay 2,3,4,6,7,8': 'San Antonio Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'Brgy. Asis-3 EC', 'Sampaloc': 'Brgy. Asis-3 EC', 'Santa Maria, Balas, &amp; Buco': 'Darasa Brgy. Hall', 'Tranca': 'San Antonio Brgy. Hall'}, 'transferred': {'Aya': 'Darasa Brgy. Hall', 'Banga &amp; San Guillermo': 'Darasa Brgy. Hall', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'San Antonio Brgy. Hall', 'Poblacion Barangay 5': 'San Antonio Brgy. Hall', 'Poblacion Barangay 2,3,4,6,7,8': 'San Antonio Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'Brgy. Asis-3 EC', 'Sampaloc': 'Brgy. Asis-3 EC', 'Santa Maria, Balas, &amp; Buco': 'Darasa Brgy. Hall', 'Tranca': 'San Antonio Brgy. Hall'}, 'shelterlvl': {'Brgy. Asis-3 EC': 2, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 2, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 2, 'Darasa Brgy. Hall': 2, 'Santa Clara Brgy. Hall': 2, 'San Fernando Brgy. Hall': 2}}</t>
+  </si>
+  <si>
+    <t>126737084</t>
+  </si>
+  <si>
+    <t>1m 51.91s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Brgy. Asis-3 EC', 'Banga &amp; San Guillermo': 'City EC of Sto. Tomas', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'Tagaytay Unida Church', 'Poblacion Barangay 5': 'Tagaytay Unida Church', 'Poblacion Barangay 2,3,4,6,7,8': 'Tagaytay Unida Church', 'Quiling, Miranda, &amp; Tumaway': 'City EC of Sto. Tomas', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'Brgy. Asis-3 EC', 'Tranca': 'City EC of Sto. Tomas'}, 'transferred': {'Aya': 'Brgy. Asis-3 EC', 'Banga &amp; San Guillermo': 'City EC of Sto. Tomas', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'Tagaytay Unida Church', 'Poblacion Barangay 5': 'Tagaytay Unida Church', 'Poblacion Barangay 2,3,4,6,7,8': 'Tagaytay Unida Church', 'Quiling, Miranda, &amp; Tumaway': 'City EC of Sto. Tomas', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'Brgy. Asis-3 EC', 'Tranca': 'City EC of Sto. Tomas'}, 'shelterlvl': {'Brgy. Asis-3 EC': 2, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 2, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 2, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 2}}</t>
+  </si>
+  <si>
+    <t>126649557</t>
+  </si>
+  <si>
+    <t>1m 51.44s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Maugat Gymnasium', 'Banga &amp; San Guillermo': 'Brgy. Asis-3 EC', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'Brgy. Asis-3 EC', 'Poblacion Barangay 2,3,4,6,7,8': 'Darasa Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'Maugat Gymnasium', 'Sampaloc': 'Brgy. Asis-3 EC', 'Santa Maria, Balas, &amp; Buco': 'Darasa Brgy. Hall', 'Tranca': 'Darasa Brgy. Hall'}, 'transferred': {'Aya': 'Maugat Gymnasium', 'Banga &amp; San Guillermo': 'Brgy. Asis-3 EC', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'Brgy. Asis-3 EC', 'Poblacion Barangay 2,3,4,6,7,8': 'Darasa Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'Maugat Gymnasium', 'Sampaloc': 'Brgy. Asis-3 EC', 'Santa Maria, Balas, &amp; Buco': 'Darasa Brgy. Hall', 'Tranca': 'Darasa Brgy. Hall'}, 'shelterlvl': {'Brgy. Asis-3 EC': 2, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 2, 'Tagaytay Unida Church': 2, 'San Antonio Brgy. Hall': 2, 'Darasa Brgy. Hall': 2, 'Santa Clara Brgy. Hall': 2, 'San Fernando Brgy. Hall': 2}}</t>
+  </si>
+  <si>
+    <t>126661795</t>
+  </si>
+  <si>
+    <t>1m 51.59s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Darasa Brgy. Hall', 'Banga &amp; San Guillermo': 'Darasa Brgy. Hall', 'Caloocan &amp; Leynes': 'Suplang Covered Court', 'Poblacion Barangay 1': 'Brgy. San Jose BB Court', 'Poblacion Barangay 5': 'Brgy. San Jose BB Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Brgy. San Jose BB Court', 'Quiling, Miranda, &amp; Tumaway': 'Suplang Covered Court', 'Sampaloc': 'Darasa Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Brgy. San Jose BB Court', 'Tranca': 'Suplang Covered Court'}, 'transferred': {'Aya': 'Darasa Brgy. Hall', 'Banga &amp; San Guillermo': 'Darasa Brgy. Hall', 'Caloocan &amp; Leynes': 'Suplang Covered Court', 'Poblacion Barangay 1': 'Brgy. San Jose BB Court', 'Poblacion Barangay 5': 'Brgy. San Jose BB Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Brgy. San Jose BB Court', 'Quiling, Miranda, &amp; Tumaway': 'Suplang Covered Court', 'Sampaloc': 'Darasa Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Brgy. San Jose BB Court', 'Tranca': 'Suplang Covered Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 2, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 2, 'Brgy. San Jose BB Court': 2, 'Maugat Gymnasium': 2, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 2, 'Santa Clara Brgy. Hall': 2, 'San Fernando Brgy. Hall': 2}}</t>
+  </si>
+  <si>
+    <t>126502688</t>
+  </si>
+  <si>
+    <t>1m 52.27s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Brgy. San Jose BB Court', 'Banga &amp; San Guillermo': 'Brgy. Asis-3 EC', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'Brgy. San Jose BB Court', 'Poblacion Barangay 5': 'Suplang Covered Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Suplang Covered Court', 'Quiling, Miranda, &amp; Tumaway': 'Brgy. San Jose BB Court', 'Sampaloc': 'Brgy. Asis-3 EC', 'Santa Maria, Balas, &amp; Buco': 'Suplang Covered Court', 'Tranca': 'Suplang Covered Court'}, 'transferred': {'Aya': 'Brgy. San Jose BB Court', 'Banga &amp; San Guillermo': 'Brgy. Asis-3 EC', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'Brgy. San Jose BB Court', 'Poblacion Barangay 5': 'Suplang Covered Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Suplang Covered Court', 'Quiling, Miranda, &amp; Tumaway': 'Brgy. San Jose BB Court', 'Sampaloc': 'Brgy. Asis-3 EC', 'Santa Maria, Balas, &amp; Buco': 'Suplang Covered Court', 'Tranca': 'Suplang Covered Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 2, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 2, 'Brgy. San Jose BB Court': 2, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 2, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>126884155</t>
+  </si>
+  <si>
+    <t>1m 53.09s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'San Antonio Brgy. Hall', 'Banga &amp; San Guillermo': 'Tagaytay Unida Church', 'Caloocan &amp; Leynes': 'Darasa Brgy. Hall', 'Poblacion Barangay 1': 'San Antonio Brgy. Hall', 'Poblacion Barangay 5': 'Tagaytay Unida Church', 'Poblacion Barangay 2,3,4,6,7,8': 'Darasa Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'Tagaytay Unida Church', 'Sampaloc': 'San Antonio Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Darasa Brgy. Hall', 'Tranca': 'San Antonio Brgy. Hall'}, 'transferred': {'Aya': 'San Antonio Brgy. Hall', 'Banga &amp; San Guillermo': 'Tagaytay Unida Church', 'Caloocan &amp; Leynes': 'Darasa Brgy. Hall', 'Poblacion Barangay 1': 'San Antonio Brgy. Hall', 'Poblacion Barangay 5': 'Tagaytay Unida Church', 'Poblacion Barangay 2,3,4,6,7,8': 'Darasa Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'Tagaytay Unida Church', 'Sampaloc': 'San Antonio Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Darasa Brgy. Hall', 'Tranca': 'San Antonio Brgy. Hall'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 2, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 2, 'San Antonio Brgy. Hall': 2, 'Darasa Brgy. Hall': 2, 'Santa Clara Brgy. Hall': 2, 'San Fernando Brgy. Hall': 2}}</t>
+  </si>
+  <si>
+    <t>126648038</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Suplang Covered Court', 'Banga &amp; San Guillermo': 'City EC of Sto. Tomas', 'Caloocan &amp; Leynes': 'City EC of Sto. Tomas', 'Poblacion Barangay 1': 'Suplang Covered Court', 'Poblacion Barangay 5': 'Brgy. San Jose BB Court', 'Poblacion Barangay 2,3,4,6,7,8': 'City EC of Sto. Tomas', 'Quiling, Miranda, &amp; Tumaway': 'Brgy. San Jose BB Court', 'Sampaloc': 'Brgy. San Jose BB Court', 'Santa Maria, Balas, &amp; Buco': 'Suplang Covered Court', 'Tranca': 'Suplang Covered Court'}, 'transferred': {'Aya': 'Suplang Covered Court', 'Banga &amp; San Guillermo': 'City EC of Sto. Tomas', 'Caloocan &amp; Leynes': 'City EC of Sto. Tomas', 'Poblacion Barangay 1': 'Suplang Covered Court', 'Poblacion Barangay 5': 'Brgy. San Jose BB Court', 'Poblacion Barangay 2,3,4,6,7,8': 'City EC of Sto. Tomas', 'Quiling, Miranda, &amp; Tumaway': 'Brgy. San Jose BB Court', 'Sampaloc': 'Brgy. San Jose BB Court', 'Santa Maria, Balas, &amp; Buco': 'Suplang Covered Court', 'Tranca': 'Suplang Covered Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 2, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 2, 'Brgy. San Jose BB Court': 2, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 2, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 2}}</t>
+  </si>
+  <si>
+    <t>126607891</t>
+  </si>
+  <si>
+    <t>1m 51.50s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Maugat Gymnasium', 'Banga &amp; San Guillermo': 'Maugat Gymnasium', 'Caloocan &amp; Leynes': 'Maugat Gymnasium', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'Darasa Brgy. Hall', 'Poblacion Barangay 2,3,4,6,7,8': 'Brgy. San Jose BB Court', 'Quiling, Miranda, &amp; Tumaway': 'Brgy. San Jose BB Court', 'Sampaloc': 'Darasa Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Darasa Brgy. Hall', 'Tranca': 'Darasa Brgy. Hall'}, 'transferred': {'Aya': 'Maugat Gymnasium', 'Banga &amp; San Guillermo': 'Maugat Gymnasium', 'Caloocan &amp; Leynes': 'Maugat Gymnasium', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'Darasa Brgy. Hall', 'Poblacion Barangay 2,3,4,6,7,8': 'Brgy. San Jose BB Court', 'Quiling, Miranda, &amp; Tumaway': 'Brgy. San Jose BB Court', 'Sampaloc': 'Darasa Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Darasa Brgy. Hall', 'Tranca': 'Darasa Brgy. Hall'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 2, 'Maugat Gymnasium': 2, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 2, 'Santa Clara Brgy. Hall': 2, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>126577143</t>
+  </si>
+  <si>
+    <t>1m 51.98s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Brgy. San Jose BB Court', 'Banga &amp; San Guillermo': 'City EC of Sto. Tomas', 'Caloocan &amp; Leynes': 'Brgy. San Jose BB Court', 'Poblacion Barangay 1': 'Tagaytay Unida Church', 'Poblacion Barangay 5': 'Tagaytay Unida Church', 'Poblacion Barangay 2,3,4,6,7,8': 'Tagaytay Unida Church', 'Quiling, Miranda, &amp; Tumaway': 'City EC of Sto. Tomas', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'Brgy. San Jose BB Court', 'Tranca': 'Brgy. San Jose BB Court'}, 'transferred': {'Aya': 'Brgy. San Jose BB Court', 'Banga &amp; San Guillermo': 'City EC of Sto. Tomas', 'Caloocan &amp; Leynes': 'Brgy. San Jose BB Court', 'Poblacion Barangay 1': 'Tagaytay Unida Church', 'Poblacion Barangay 5': 'Tagaytay Unida Church', 'Poblacion Barangay 2,3,4,6,7,8': 'Tagaytay Unida Church', 'Quiling, Miranda, &amp; Tumaway': 'City EC of Sto. Tomas', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'Brgy. San Jose BB Court', 'Tranca': 'Brgy. San Jose BB Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 2, 'Brgy. San Jose BB Court': 2, 'Maugat Gymnasium': 2, 'Tagaytay Unida Church': 2, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>97048308</t>
+  </si>
+  <si>
+    <t>1m 31.90s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Suplang Covered Court', 'Banga &amp; San Guillermo': 'Brgy. San Jose BB Court', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'Suplang Covered Court', 'Poblacion Barangay 5': 'Brgy. Asis-3 EC', 'Poblacion Barangay 2,3,4,6,7,8': 'Maugat Gymnasium', 'Quiling, Miranda, &amp; Tumaway': 'Brgy. San Jose BB Court', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'Tagaytay Unida Church', 'Tranca': 'Brgy. San Jose BB Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 2, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 2, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>97133449</t>
+  </si>
+  <si>
+    <t>1m 32.20s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'City EC of Sto. Tomas', 'Banga &amp; San Guillermo': 'Brgy. San Jose BB Court', 'Caloocan &amp; Leynes': 'Tagaytay Unida Church', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'Maugat Gymnasium', 'Poblacion Barangay 2,3,4,6,7,8': 'Suplang Covered Court', 'Quiling, Miranda, &amp; Tumaway': 'City EC of Sto. Tomas', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'Maugat Gymnasium', 'Tranca': 'Brgy. San Jose BB Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 2, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 2, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 2, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>97074250</t>
+  </si>
+  <si>
+    <t>1m 32.28s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Maugat Gymnasium', 'Banga &amp; San Guillermo': 'Brgy. Asis-3 EC', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'Brgy. San Jose BB Court', 'Poblacion Barangay 5': 'Brgy. San Jose BB Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Suplang Covered Court', 'Quiling, Miranda, &amp; Tumaway': 'Suplang Covered Court', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'Tagaytay Unida Church', 'Tranca': 'Brgy. San Jose BB Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 2, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>97061367</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Maugat Gymnasium', 'Banga &amp; San Guillermo': 'Brgy. San Jose BB Court', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'Brgy. Asis-3 EC', 'Poblacion Barangay 2,3,4,6,7,8': 'Suplang Covered Court', 'Quiling, Miranda, &amp; Tumaway': 'Suplang Covered Court', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'Tagaytay Unida Church', 'Tranca': 'Brgy. San Jose BB Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 2, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 2, 'Santa Clara Brgy. Hall': 2, 'San Fernando Brgy. Hall': 2}}</t>
+  </si>
+  <si>
+    <t>97121771</t>
+  </si>
+  <si>
+    <t>1m 32.25s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'City EC of Sto. Tomas', 'Banga &amp; San Guillermo': 'Suplang Covered Court', 'Caloocan &amp; Leynes': 'Tagaytay Unida Church', 'Poblacion Barangay 1': 'Brgy. San Jose BB Court', 'Poblacion Barangay 5': 'Brgy. San Jose BB Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Maugat Gymnasium', 'Quiling, Miranda, &amp; Tumaway': 'City EC of Sto. Tomas', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'Brgy. San Jose BB Court', 'Tranca': 'Suplang Covered Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 2, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 2, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 2}}</t>
+  </si>
+  <si>
+    <t>97070281</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Maugat Gymnasium', 'Banga &amp; San Guillermo': 'Tagaytay Unida Church', 'Caloocan &amp; Leynes': 'Tagaytay Unida Church', 'Poblacion Barangay 1': 'Brgy. San Jose BB Court', 'Poblacion Barangay 5': 'Brgy. San Jose BB Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Suplang Covered Court', 'Quiling, Miranda, &amp; Tumaway': 'Suplang Covered Court', 'Sampaloc': 'Brgy. Asis-3 EC', 'Santa Maria, Balas, &amp; Buco': 'Brgy. Asis-3 EC', 'Tranca': 'Brgy. San Jose BB Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 2, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 2, 'Darasa Brgy. Hall': 2, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 2}}</t>
+  </si>
+  <si>
+    <t>1m 32.54s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Maugat Gymnasium', 'Banga &amp; San Guillermo': 'Tagaytay Unida Church', 'Caloocan &amp; Leynes': 'Tagaytay Unida Church', 'Poblacion Barangay 1': 'Brgy. San Jose BB Court', 'Poblacion Barangay 5': 'Brgy. San Jose BB Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Suplang Covered Court', 'Quiling, Miranda, &amp; Tumaway': 'Suplang Covered Court', 'Sampaloc': 'Brgy. Asis-3 EC', 'Santa Maria, Balas, &amp; Buco': 'Brgy. Asis-3 EC', 'Tranca': 'Brgy. San Jose BB Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 2, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 2, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>97065407</t>
+  </si>
+  <si>
+    <t>1m 32.09s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'City EC of Sto. Tomas', 'Banga &amp; San Guillermo': 'Suplang Covered Court', 'Caloocan &amp; Leynes': 'Tagaytay Unida Church', 'Poblacion Barangay 1': 'Brgy. San Jose BB Court', 'Poblacion Barangay 5': 'Brgy. San Jose BB Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Maugat Gymnasium', 'Quiling, Miranda, &amp; Tumaway': 'Suplang Covered Court', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'Brgy. San Jose BB Court', 'Tranca': 'Suplang Covered Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 2, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 2, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 2}}</t>
+  </si>
+  <si>
+    <t>97088840</t>
+  </si>
+  <si>
+    <t>1m 32.13s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Maugat Gymnasium', 'Banga &amp; San Guillermo': 'Brgy. San Jose BB Court', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'Brgy. San Jose BB Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Tagaytay Unida Church', 'Quiling, Miranda, &amp; Tumaway': 'Suplang Covered Court', 'Sampaloc': 'Brgy. Asis-3 EC', 'Santa Maria, Balas, &amp; Buco': 'Suplang Covered Court', 'Tranca': 'Suplang Covered Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 2, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 2, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 2}}</t>
+  </si>
+  <si>
+    <t>97140855</t>
+  </si>
+  <si>
+    <t>1m 32.06s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Maugat Gymnasium', 'Banga &amp; San Guillermo': 'Tagaytay Unida Church', 'Caloocan &amp; Leynes': 'Tagaytay Unida Church', 'Poblacion Barangay 1': 'Brgy. San Jose BB Court', 'Poblacion Barangay 5': 'Brgy. San Jose BB Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Suplang Covered Court', 'Quiling, Miranda, &amp; Tumaway': 'Suplang Covered Court', 'Sampaloc': 'Brgy. San Jose BB Court', 'Santa Maria, Balas, &amp; Buco': 'City EC of Sto. Tomas', 'Tranca': 'City EC of Sto. Tomas'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 2, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 2, 'Darasa Brgy. Hall': 2, 'Santa Clara Brgy. Hall': 2, 'San Fernando Brgy. Hall': 2}}</t>
+  </si>
+  <si>
+    <t>202500000000000175112192</t>
+  </si>
+  <si>
+    <t>2m 16.81s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Brgy. San Jose BB Court', 'Banga &amp; San Guillermo': 'City EC of Sto. Tomas', 'Caloocan &amp; Leynes': 'Maugat Gymnasium', 'Poblacion Barangay 1': 'Santa Clara Brgy. Hall', 'Poblacion Barangay 5': 'Suplang Covered Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Darasa Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'Tagaytay Unida Church', 'Sampaloc': 'Maugat Gymnasium', 'Santa Maria, Balas, &amp; Buco': 'Santa Clara Brgy. Hall', 'Tranca': 'Suplang Covered Court'}, 'transferred': {'Aya': 'San Fernando Brgy. Hall', 'Banga &amp; San Guillermo': 'San Antonio Brgy. Hall', 'Caloocan &amp; Leynes': 'San Antonio Brgy. Hall', 'Poblacion Barangay 1': 'San Antonio Brgy. Hall', 'Poblacion Barangay 5': 'San Antonio Brgy. Hall', 'Poblacion Barangay 2,3,4,6,7,8': 'San Fernando Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'San Fernando Brgy. Hall', 'Sampaloc': 'San Fernando Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'San Antonio Brgy. Hall', 'Tranca': 'San Fernando Brgy. Hall'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 2, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 2}}</t>
+  </si>
+  <si>
+    <t>2m 16.84s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Santa Clara Brgy. Hall', 'Banga &amp; San Guillermo': 'City EC of Sto. Tomas', 'Caloocan &amp; Leynes': 'City EC of Sto. Tomas', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'Maugat Gymnasium', 'Poblacion Barangay 2,3,4,6,7,8': 'Suplang Covered Court', 'Quiling, Miranda, &amp; Tumaway': 'San Antonio Brgy. Hall', 'Sampaloc': 'Darasa Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Maugat Gymnasium', 'Tranca': 'Darasa Brgy. Hall'}, 'transferred': {'Aya': 'Brgy. Asis-3 EC', 'Banga &amp; San Guillermo': 'Tagaytay Unida Church', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'Tagaytay Unida Church', 'Poblacion Barangay 5': 'Tagaytay Unida Church', 'Poblacion Barangay 2,3,4,6,7,8': 'Brgy. Asis-3 EC', 'Quiling, Miranda, &amp; Tumaway': 'Brgy. Asis-3 EC', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'Tagaytay Unida Church', 'Tranca': 'Tagaytay Unida Church'}, 'shelterlvl': {'Brgy. Asis-3 EC': 2, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 2, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>23m 8.96s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Darasa Brgy. Hall', 'Banga &amp; San Guillermo': 'Brgy. San Jose BB Court', 'Caloocan &amp; Leynes': 'Suplang Covered Court', 'Poblacion Barangay 1': 'Suplang Covered Court', 'Poblacion Barangay 5': 'Santa Clara Brgy. Hall', 'Poblacion Barangay 2,3,4,6,7,8': 'San Fernando Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'San Antonio Brgy. Hall', 'Sampaloc': 'Santa Clara Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Tagaytay Unida Church', 'Tranca': 'Tagaytay Unida Church'}, 'transferred': {'Aya': 'Maugat Gymnasium', 'Banga &amp; San Guillermo': 'City EC of Sto. Tomas', 'Caloocan &amp; Leynes': 'Maugat Gymnasium', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'Maugat Gymnasium', 'Poblacion Barangay 2,3,4,6,7,8': 'City EC of Sto. Tomas', 'Quiling, Miranda, &amp; Tumaway': 'Maugat Gymnasium', 'Sampaloc': 'Maugat Gymnasium', 'Santa Maria, Balas, &amp; Buco': 'Maugat Gymnasium', 'Tranca': 'City EC of Sto. Tomas'}, 'shelterlvl': {'Brgy. Asis-3 EC': 2, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 2, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>2m 17.29s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Brgy. Asis-3 EC', 'Banga &amp; San Guillermo': 'City EC of Sto. Tomas', 'Caloocan &amp; Leynes': 'Santa Clara Brgy. Hall', 'Poblacion Barangay 1': 'Brgy. San Jose BB Court', 'Poblacion Barangay 5': 'City EC of Sto. Tomas', 'Poblacion Barangay 2,3,4,6,7,8': 'Maugat Gymnasium', 'Quiling, Miranda, &amp; Tumaway': 'Tagaytay Unida Church', 'Sampaloc': 'Brgy. San Jose BB Court', 'Santa Maria, Balas, &amp; Buco': 'Darasa Brgy. Hall', 'Tranca': 'Darasa Brgy. Hall'}, 'transferred': {'Aya': 'San Antonio Brgy. Hall', 'Banga &amp; San Guillermo': 'Suplang Covered Court', 'Caloocan &amp; Leynes': 'San Antonio Brgy. Hall', 'Poblacion Barangay 1': 'Suplang Covered Court', 'Poblacion Barangay 5': 'Suplang Covered Court', 'Poblacion Barangay 2,3,4,6,7,8': 'San Antonio Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'San Antonio Brgy. Hall', 'Sampaloc': 'Suplang Covered Court', 'Santa Maria, Balas, &amp; Buco': 'Suplang Covered Court', 'Tranca': 'Suplang Covered Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 2, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 2, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 2}}</t>
+  </si>
+  <si>
+    <t>2m 17.58s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'San Fernando Brgy. Hall', 'Banga &amp; San Guillermo': 'Darasa Brgy. Hall', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'Suplang Covered Court', 'Poblacion Barangay 5': 'Suplang Covered Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Santa Clara Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'Maugat Gymnasium', 'Sampaloc': 'Suplang Covered Court', 'Santa Maria, Balas, &amp; Buco': 'Brgy. San Jose BB Court', 'Tranca': 'Brgy. Asis-3 EC'}, 'transferred': {'Aya': 'City EC of Sto. Tomas', 'Banga &amp; San Guillermo': 'San Antonio Brgy. Hall', 'Caloocan &amp; Leynes': 'San Antonio Brgy. Hall', 'Poblacion Barangay 1': 'San Antonio Brgy. Hall', 'Poblacion Barangay 5': 'City EC of Sto. Tomas', 'Poblacion Barangay 2,3,4,6,7,8': 'City EC of Sto. Tomas', 'Quiling, Miranda, &amp; Tumaway': 'San Antonio Brgy. Hall', 'Sampaloc': 'City EC of Sto. Tomas', 'Santa Maria, Balas, &amp; Buco': 'City EC of Sto. Tomas', 'Tranca': 'City EC of Sto. Tomas'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 2, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 2, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>2m 17.91s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'San Antonio Brgy. Hall', 'Banga &amp; San Guillermo': 'Brgy. Asis-3 EC', 'Caloocan &amp; Leynes': 'Brgy. Asis-3 EC', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'San Antonio Brgy. Hall', 'Poblacion Barangay 2,3,4,6,7,8': 'City EC of Sto. Tomas', 'Quiling, Miranda, &amp; Tumaway': 'Darasa Brgy. Hall', 'Sampaloc': 'Brgy. San Jose BB Court', 'Santa Maria, Balas, &amp; Buco': 'Suplang Covered Court', 'Tranca': 'Brgy. San Jose BB Court'}, 'transferred': {'Aya': 'Tagaytay Unida Church', 'Banga &amp; San Guillermo': 'Santa Clara Brgy. Hall', 'Caloocan &amp; Leynes': 'Tagaytay Unida Church', 'Poblacion Barangay 1': 'Tagaytay Unida Church', 'Poblacion Barangay 5': 'Santa Clara Brgy. Hall', 'Poblacion Barangay 2,3,4,6,7,8': 'Santa Clara Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'Santa Clara Brgy. Hall', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'Santa Clara Brgy. Hall', 'Tranca': 'Santa Clara Brgy. Hall'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 2, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 2, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>2m 17.95s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'San Fernando Brgy. Hall', 'Banga &amp; San Guillermo': 'Suplang Covered Court', 'Caloocan &amp; Leynes': 'Tagaytay Unida Church', 'Poblacion Barangay 1': 'Tagaytay Unida Church', 'Poblacion Barangay 5': 'Suplang Covered Court', 'Poblacion Barangay 2,3,4,6,7,8': 'City EC of Sto. Tomas', 'Quiling, Miranda, &amp; Tumaway': 'Brgy. San Jose BB Court', 'Sampaloc': 'Brgy. Asis-3 EC', 'Santa Maria, Balas, &amp; Buco': 'Maugat Gymnasium', 'Tranca': 'Brgy. Asis-3 EC'}, 'transferred': {'Aya': 'San Antonio Brgy. Hall', 'Banga &amp; San Guillermo': 'San Antonio Brgy. Hall', 'Caloocan &amp; Leynes': 'San Antonio Brgy. Hall', 'Poblacion Barangay 1': 'San Antonio Brgy. Hall', 'Poblacion Barangay 5': 'San Antonio Brgy. Hall', 'Poblacion Barangay 2,3,4,6,7,8': 'Santa Clara Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'Santa Clara Brgy. Hall', 'Sampaloc': 'Santa Clara Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'San Antonio Brgy. Hall', 'Tranca': 'San Antonio Brgy. Hall'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 2, 'Darasa Brgy. Hall': 2, 'Santa Clara Brgy. Hall': 2, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>2m 17.23s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'San Antonio Brgy. Hall', 'Banga &amp; San Guillermo': 'Darasa Brgy. Hall', 'Caloocan &amp; Leynes': 'Suplang Covered Court', 'Poblacion Barangay 1': 'Santa Clara Brgy. Hall', 'Poblacion Barangay 5': 'Brgy. Asis-3 EC', 'Poblacion Barangay 2,3,4,6,7,8': 'City EC of Sto. Tomas', 'Quiling, Miranda, &amp; Tumaway': 'Tagaytay Unida Church', 'Sampaloc': 'Brgy. Asis-3 EC', 'Santa Maria, Balas, &amp; Buco': 'Santa Clara Brgy. Hall', 'Tranca': 'Suplang Covered Court'}, 'transferred': {'Aya': 'Brgy. San Jose BB Court', 'Banga &amp; San Guillermo': 'Maugat Gymnasium', 'Caloocan &amp; Leynes': 'Maugat Gymnasium', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'Brgy. San Jose BB Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Brgy. San Jose BB Court', 'Quiling, Miranda, &amp; Tumaway': 'Brgy. San Jose BB Court', 'Sampaloc': 'Maugat Gymnasium', 'Santa Maria, Balas, &amp; Buco': 'Maugat Gymnasium', 'Tranca': 'Brgy. San Jose BB Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 2, 'Maugat Gymnasium': 2, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>2m 17.20s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'Brgy. Asis-3 EC', 'Banga &amp; San Guillermo': 'San Fernando Brgy. Hall', 'Caloocan &amp; Leynes': 'Brgy. San Jose BB Court', 'Poblacion Barangay 1': 'Brgy. Asis-3 EC', 'Poblacion Barangay 5': 'Suplang Covered Court', 'Poblacion Barangay 2,3,4,6,7,8': 'City EC of Sto. Tomas', 'Quiling, Miranda, &amp; Tumaway': 'Santa Clara Brgy. Hall', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'Suplang Covered Court', 'Tranca': 'San Fernando Brgy. Hall'}, 'transferred': {'Aya': 'Darasa Brgy. Hall', 'Banga &amp; San Guillermo': 'Maugat Gymnasium', 'Caloocan &amp; Leynes': 'Maugat Gymnasium', 'Poblacion Barangay 1': 'Maugat Gymnasium', 'Poblacion Barangay 5': 'Darasa Brgy. Hall', 'Poblacion Barangay 2,3,4,6,7,8': 'Maugat Gymnasium', 'Quiling, Miranda, &amp; Tumaway': 'Darasa Brgy. Hall', 'Sampaloc': 'Darasa Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Maugat Gymnasium', 'Tranca': 'Darasa Brgy. Hall'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 1, 'Maugat Gymnasium': 2, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 2, 'Santa Clara Brgy. Hall': 1, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+  <si>
+    <t>2m 17.62s</t>
+  </si>
+  <si>
+    <t>{'initial': {'Aya': 'San Antonio Brgy. Hall', 'Banga &amp; San Guillermo': 'Suplang Covered Court', 'Caloocan &amp; Leynes': 'Darasa Brgy. Hall', 'Poblacion Barangay 1': 'San Antonio Brgy. Hall', 'Poblacion Barangay 5': 'Brgy. Asis-3 EC', 'Poblacion Barangay 2,3,4,6,7,8': 'Tagaytay Unida Church', 'Quiling, Miranda, &amp; Tumaway': 'Maugat Gymnasium', 'Sampaloc': 'San Fernando Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Darasa Brgy. Hall', 'Tranca': 'Suplang Covered Court'}, 'transferred': {'Aya': 'Brgy. San Jose BB Court', 'Banga &amp; San Guillermo': 'Brgy. San Jose BB Court', 'Caloocan &amp; Leynes': 'Santa Clara Brgy. Hall', 'Poblacion Barangay 1': 'Santa Clara Brgy. Hall', 'Poblacion Barangay 5': 'Brgy. San Jose BB Court', 'Poblacion Barangay 2,3,4,6,7,8': 'Brgy. San Jose BB Court', 'Quiling, Miranda, &amp; Tumaway': 'Santa Clara Brgy. Hall', 'Sampaloc': 'Santa Clara Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Brgy. San Jose BB Court', 'Tranca': 'Brgy. San Jose BB Court'}, 'shelterlvl': {'Brgy. Asis-3 EC': 1, 'City EC of Sto. Tomas': 1, 'Suplang Covered Court': 1, 'Brgy. San Jose BB Court': 2, 'Maugat Gymnasium': 1, 'Tagaytay Unida Church': 1, 'San Antonio Brgy. Hall': 1, 'Darasa Brgy. Hall': 1, 'Santa Clara Brgy. Hall': 2, 'San Fernando Brgy. Hall': 1}}</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -50,81 +374,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -412,85 +677,798 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="48.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fitness</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Gen Last Updated</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Runtime</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Allocation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>202500000000000040894464</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0m 11.81s</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>{'initial': {'Aya': 'Santa Clara Brgy. Hall', 'Banga &amp; San Guillermo': 'Brgy. San Jose BB Court', 'Caloocan &amp; Leynes': 'City EC of Sto. Tomas', 'Poblacion Barangay 1': 'Tagaytay Unida Church', 'Poblacion Barangay 5': 'Tagaytay Unida Church', 'Poblacion Barangay 2,3,4,6,7,8': 'Suplang Covered Court', 'Quiling, Miranda, &amp; Tumaway': 'Darasa Brgy. Hall', 'Sampaloc': 'Tagaytay Unida Church', 'Santa Maria, Balas, &amp; Buco': 'City EC of Sto. Tomas', 'Tranca': 'Brgy. San Jose BB Court'}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>202500000000000040894464</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8">
         <v>11</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0m 11.66s</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>{'initial': {'Aya': 'San Antonio Brgy. Hall', 'Banga &amp; San Guillermo': 'Brgy. San Jose BB Court', 'Caloocan &amp; Leynes': 'Darasa Brgy. Hall', 'Poblacion Barangay 1': 'Brgy. Asis-3 EC', 'Poblacion Barangay 5': 'Brgy. Asis-3 EC', 'Poblacion Barangay 2,3,4,6,7,8': 'Santa Clara Brgy. Hall', 'Quiling, Miranda, &amp; Tumaway': 'City EC of Sto. Tomas', 'Sampaloc': 'Darasa Brgy. Hall', 'Santa Maria, Balas, &amp; Buco': 'Brgy. Asis-3 EC', 'Tranca': 'Brgy. San Jose BB Court'}}</t>
-        </is>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="51.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2">
+        <v>1879</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3">
+        <v>3428</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4">
+        <v>987</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5">
+        <v>792</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6">
+        <v>103</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7">
+        <v>833</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8">
+        <v>709</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9">
+        <v>103</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10">
+        <v>84</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11">
+        <v>2137</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2">
+        <v>1307</v>
+      </c>
+      <c r="D2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3">
+        <v>3519</v>
+      </c>
+      <c r="D3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4">
+        <v>1800</v>
+      </c>
+      <c r="D4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5">
+        <v>4676</v>
+      </c>
+      <c r="D5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6">
+        <v>479</v>
+      </c>
+      <c r="D6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7">
+        <v>2085</v>
+      </c>
+      <c r="D7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8">
+        <v>197</v>
+      </c>
+      <c r="D8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9">
+        <v>1836</v>
+      </c>
+      <c r="D9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10">
+        <v>3545</v>
+      </c>
+      <c r="D10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11">
+        <v>2611</v>
+      </c>
+      <c r="D11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="34.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2">
+        <v>270</v>
+      </c>
+      <c r="D2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3">
+        <v>234</v>
+      </c>
+      <c r="D3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4">
+        <v>848</v>
+      </c>
+      <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5">
+        <v>1822</v>
+      </c>
+      <c r="D5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6">
+        <v>671</v>
+      </c>
+      <c r="D6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7">
+        <v>1565</v>
+      </c>
+      <c r="D7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8">
+        <v>4665</v>
+      </c>
+      <c r="D8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10">
+        <v>440</v>
+      </c>
+      <c r="D10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11">
+        <v>632</v>
+      </c>
+      <c r="D11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
